--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260727.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.68%</t>
+          <t>10.62%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.28%</t>
+          <t>10.27%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.52%</t>
+          <t>8.54%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>7.25%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.70%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>77,920</t>
+          <t>11,472</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,472</t>
+          <t>77,920</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1232,73 +1232,73 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>4,980</t>
+          <t>75,970</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,112</t>
+          <t>4,980</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>75,970</t>
+          <t>9,112</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>103,135,552</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
